--- a/content-sources/medical-tests-reconcile.xlsx
+++ b/content-sources/medical-tests-reconcile.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="102">
   <si>
     <t>issue_type</t>
   </si>
@@ -157,6 +157,12 @@
     <t>Mikrobiota jelitowa</t>
   </si>
   <si>
+    <t>Lipoprotein(a)</t>
+  </si>
+  <si>
+    <t>Zonulina</t>
+  </si>
+  <si>
     <t>Thromboplastin</t>
   </si>
   <si>
@@ -199,18 +205,6 @@
     <t>Fibrynogen</t>
   </si>
   <si>
-    <t>DUPLICATE</t>
-  </si>
-  <si>
-    <t>Lipoprotein(a)</t>
-  </si>
-  <si>
-    <t>Lp(a)</t>
-  </si>
-  <si>
-    <t>Rename one occurrence in the EN sheet to disambiguate (affects URL slug).</t>
-  </si>
-  <si>
     <t>CA-125 Tumor Marker</t>
   </si>
   <si>
@@ -323,24 +317,6 @@
   </si>
   <si>
     <t>ISI (Insomnia Severity Index)</t>
-  </si>
-  <si>
-    <t>MISSING_EN</t>
-  </si>
-  <si>
-    <t>Rosenberg Self-Esteem Scale</t>
-  </si>
-  <si>
-    <t>Add EN translation, or remove the PL row if intentionally PL-only.</t>
-  </si>
-  <si>
-    <t>PHQ-A (Patient Health Questionnaire - Adolescent)</t>
-  </si>
-  <si>
-    <t>GAD-2 + PHQ-2 (Ultra-Brief Screening)</t>
-  </si>
-  <si>
-    <t>SCOFF (Eating Disorder Screen)</t>
   </si>
 </sst>
 </file>
@@ -717,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1215,10 +1191,10 @@
         <v>7</v>
       </c>
       <c r="B22">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
@@ -1238,10 +1214,10 @@
         <v>7</v>
       </c>
       <c r="B23">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
         <v>50</v>
@@ -1261,10 +1237,10 @@
         <v>7</v>
       </c>
       <c r="B24">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
         <v>52</v>
@@ -1284,10 +1260,10 @@
         <v>7</v>
       </c>
       <c r="B25">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
         <v>54</v>
@@ -1307,10 +1283,10 @@
         <v>7</v>
       </c>
       <c r="B26">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
         <v>56</v>
@@ -1330,10 +1306,10 @@
         <v>7</v>
       </c>
       <c r="B27">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
         <v>58</v>
@@ -1353,10 +1329,10 @@
         <v>7</v>
       </c>
       <c r="B28">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
         <v>60</v>
@@ -1373,22 +1349,22 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29">
+        <v>61</v>
+      </c>
+      <c r="C29">
+        <v>61</v>
+      </c>
+      <c r="D29" t="s">
         <v>62</v>
       </c>
-      <c r="B29">
+      <c r="E29" t="s">
         <v>63</v>
       </c>
-      <c r="C29">
-        <v>63</v>
-      </c>
-      <c r="D29" t="s">
-        <v>63</v>
-      </c>
-      <c r="E29" t="s">
-        <v>64</v>
-      </c>
       <c r="F29" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
@@ -1405,10 +1381,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F30" t="s">
         <v>10</v>
@@ -1428,10 +1404,10 @@
         <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F31" t="s">
         <v>10</v>
@@ -1451,10 +1427,10 @@
         <v>71</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F32" t="s">
         <v>10</v>
@@ -1474,10 +1450,10 @@
         <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F33" t="s">
         <v>10</v>
@@ -1497,10 +1473,10 @@
         <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F34" t="s">
         <v>10</v>
@@ -1520,10 +1496,10 @@
         <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s">
         <v>10</v>
@@ -1543,10 +1519,10 @@
         <v>77</v>
       </c>
       <c r="D36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F36" t="s">
         <v>10</v>
@@ -1566,10 +1542,10 @@
         <v>78</v>
       </c>
       <c r="D37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F37" t="s">
         <v>10</v>
@@ -1589,10 +1565,10 @@
         <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -1612,10 +1588,10 @@
         <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -1635,10 +1611,10 @@
         <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F40" t="s">
         <v>10</v>
@@ -1658,10 +1634,10 @@
         <v>82</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F41" t="s">
         <v>10</v>
@@ -1681,10 +1657,10 @@
         <v>83</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E42" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -1704,10 +1680,10 @@
         <v>84</v>
       </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E43" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F43" t="s">
         <v>10</v>
@@ -1727,10 +1703,10 @@
         <v>85</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F44" t="s">
         <v>10</v>
@@ -1750,10 +1726,10 @@
         <v>86</v>
       </c>
       <c r="D45" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E45" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F45" t="s">
         <v>10</v>
@@ -1773,10 +1749,10 @@
         <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F46" t="s">
         <v>10</v>
@@ -1796,10 +1772,10 @@
         <v>89</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E47" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F47" t="s">
         <v>10</v>
@@ -1819,10 +1795,10 @@
         <v>90</v>
       </c>
       <c r="D48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E48" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F48" t="s">
         <v>10</v>
@@ -1842,10 +1818,10 @@
         <v>92</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F49" t="s">
         <v>10</v>
@@ -1865,10 +1841,10 @@
         <v>93</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F50" t="s">
         <v>10</v>
@@ -1888,10 +1864,10 @@
         <v>94</v>
       </c>
       <c r="D51" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E51" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F51" t="s">
         <v>10</v>
@@ -1911,107 +1887,15 @@
         <v>95</v>
       </c>
       <c r="D52" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E52" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F52" t="s">
         <v>10</v>
       </c>
       <c r="G52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53">
-        <v>104</v>
-      </c>
-      <c r="C53">
-        <v>104</v>
-      </c>
-      <c r="D53" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" t="s">
-        <v>105</v>
-      </c>
-      <c r="F53" t="s">
-        <v>106</v>
-      </c>
-      <c r="G53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54">
-        <v>105</v>
-      </c>
-      <c r="C54">
-        <v>105</v>
-      </c>
-      <c r="D54" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" t="s">
-        <v>107</v>
-      </c>
-      <c r="F54" t="s">
-        <v>106</v>
-      </c>
-      <c r="G54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>104</v>
-      </c>
-      <c r="B55">
-        <v>106</v>
-      </c>
-      <c r="C55">
-        <v>106</v>
-      </c>
-      <c r="D55" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" t="s">
-        <v>108</v>
-      </c>
-      <c r="F55" t="s">
-        <v>106</v>
-      </c>
-      <c r="G55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>104</v>
-      </c>
-      <c r="B56">
-        <v>107</v>
-      </c>
-      <c r="C56">
-        <v>107</v>
-      </c>
-      <c r="D56" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" t="s">
-        <v>109</v>
-      </c>
-      <c r="F56" t="s">
-        <v>106</v>
-      </c>
-      <c r="G56" t="s">
         <v>11</v>
       </c>
     </row>

--- a/content-sources/medical-tests-reconcile.xlsx
+++ b/content-sources/medical-tests-reconcile.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="104">
   <si>
     <t>issue_type</t>
   </si>
@@ -205,24 +205,6 @@
     <t>Fibrynogen</t>
   </si>
   <si>
-    <t>CA-125 Tumor Marker</t>
-  </si>
-  <si>
-    <t>CA-125</t>
-  </si>
-  <si>
-    <t>CA 19-9 Tumor Marker</t>
-  </si>
-  <si>
-    <t>CA 19-9</t>
-  </si>
-  <si>
-    <t>RF Test</t>
-  </si>
-  <si>
-    <t>RF</t>
-  </si>
-  <si>
     <t>Thyroid Stimulating Hormone (TSH)</t>
   </si>
   <si>
@@ -292,6 +274,9 @@
     <t>PHQ-15 (Patient Health Questionnaire-15)</t>
   </si>
   <si>
+    <t>OCI-R (Obsessive-Compulsive Inventory-Revised)</t>
+  </si>
+  <si>
     <t>ASRS v1.1 (Adult ADHD Self-Report Scale)</t>
   </si>
   <si>
@@ -301,7 +286,7 @@
     <t>MDQ (Mood Disorder Questionnaire)</t>
   </si>
   <si>
-    <t>OCI-R (Obsessive-Compulsive Inventory-Revised)</t>
+    <t>DASS-21 (Depression Anxiety Stress Scales)</t>
   </si>
   <si>
     <t>PSS-10 (Perceived Stress Scale)</t>
@@ -310,13 +295,34 @@
     <t>CBI (Copenhagen Burnout Inventory)</t>
   </si>
   <si>
-    <t>DASS-21 (Depression Anxiety Stress Scales)</t>
-  </si>
-  <si>
     <t>EAT-26 (Eating Attitudes Test)</t>
   </si>
   <si>
     <t>ISI (Insomnia Severity Index)</t>
+  </si>
+  <si>
+    <t>DAST-10 (Drug Abuse Screening Test)</t>
+  </si>
+  <si>
+    <t>C-SSRS Screener (Columbia Suicide Severity Rating Scale)</t>
+  </si>
+  <si>
+    <t>K10 (Kessler Psychological Distress Scale)</t>
+  </si>
+  <si>
+    <t>AUDIT (Alcohol Use Disorders Identification Test)</t>
+  </si>
+  <si>
+    <t>PSQI (Pittsburgh Sleep Quality Index)</t>
+  </si>
+  <si>
+    <t>EPDS (Edinburgh Postnatal Depression Scale)</t>
+  </si>
+  <si>
+    <t>DASS-21 (Depression Anxiety Stress Scale)</t>
+  </si>
+  <si>
+    <t>UCLA Loneliness Scale</t>
   </si>
 </sst>
 </file>
@@ -693,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1375,10 +1381,10 @@
         <v>7</v>
       </c>
       <c r="B30">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C30">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
         <v>64</v>
@@ -1398,10 +1404,10 @@
         <v>7</v>
       </c>
       <c r="B31">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C31">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
         <v>66</v>
@@ -1421,10 +1427,10 @@
         <v>7</v>
       </c>
       <c r="B32">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C32">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
         <v>68</v>
@@ -1444,10 +1450,10 @@
         <v>7</v>
       </c>
       <c r="B33">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C33">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
         <v>70</v>
@@ -1467,10 +1473,10 @@
         <v>7</v>
       </c>
       <c r="B34">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C34">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
         <v>72</v>
@@ -1490,10 +1496,10 @@
         <v>7</v>
       </c>
       <c r="B35">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C35">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
         <v>74</v>
@@ -1513,10 +1519,10 @@
         <v>7</v>
       </c>
       <c r="B36">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C36">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
         <v>76</v>
@@ -1536,10 +1542,10 @@
         <v>7</v>
       </c>
       <c r="B37">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C37">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
         <v>78</v>
@@ -1559,10 +1565,10 @@
         <v>7</v>
       </c>
       <c r="B38">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C38">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
         <v>80</v>
@@ -1582,16 +1588,16 @@
         <v>7</v>
       </c>
       <c r="B39">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C39">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
         <v>82</v>
       </c>
       <c r="E39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -1605,16 +1611,16 @@
         <v>7</v>
       </c>
       <c r="B40">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C40">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E40" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F40" t="s">
         <v>10</v>
@@ -1628,16 +1634,16 @@
         <v>7</v>
       </c>
       <c r="B41">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C41">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E41" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F41" t="s">
         <v>10</v>
@@ -1651,16 +1657,16 @@
         <v>7</v>
       </c>
       <c r="B42">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C42">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E42" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -1674,16 +1680,16 @@
         <v>7</v>
       </c>
       <c r="B43">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C43">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D43" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E43" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F43" t="s">
         <v>10</v>
@@ -1697,16 +1703,16 @@
         <v>7</v>
       </c>
       <c r="B44">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C44">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E44" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F44" t="s">
         <v>10</v>
@@ -1720,16 +1726,16 @@
         <v>7</v>
       </c>
       <c r="B45">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C45">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D45" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F45" t="s">
         <v>10</v>
@@ -1743,16 +1749,16 @@
         <v>7</v>
       </c>
       <c r="B46">
+        <v>90</v>
+      </c>
+      <c r="C46">
+        <v>90</v>
+      </c>
+      <c r="D46" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" t="s">
         <v>87</v>
-      </c>
-      <c r="C46">
-        <v>87</v>
-      </c>
-      <c r="D46" t="s">
-        <v>92</v>
-      </c>
-      <c r="E46" t="s">
-        <v>91</v>
       </c>
       <c r="F46" t="s">
         <v>10</v>
@@ -1766,16 +1772,16 @@
         <v>7</v>
       </c>
       <c r="B47">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C47">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D47" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E47" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F47" t="s">
         <v>10</v>
@@ -1789,16 +1795,16 @@
         <v>7</v>
       </c>
       <c r="B48">
+        <v>92</v>
+      </c>
+      <c r="C48">
+        <v>92</v>
+      </c>
+      <c r="D48" t="s">
+        <v>92</v>
+      </c>
+      <c r="E48" t="s">
         <v>90</v>
-      </c>
-      <c r="C48">
-        <v>90</v>
-      </c>
-      <c r="D48" t="s">
-        <v>95</v>
-      </c>
-      <c r="E48" t="s">
-        <v>96</v>
       </c>
       <c r="F48" t="s">
         <v>10</v>
@@ -1812,16 +1818,16 @@
         <v>7</v>
       </c>
       <c r="B49">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C49">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E49" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F49" t="s">
         <v>10</v>
@@ -1835,16 +1841,16 @@
         <v>7</v>
       </c>
       <c r="B50">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C50">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D50" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E50" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F50" t="s">
         <v>10</v>
@@ -1858,16 +1864,16 @@
         <v>7</v>
       </c>
       <c r="B51">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C51">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E51" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F51" t="s">
         <v>10</v>
@@ -1881,21 +1887,182 @@
         <v>7</v>
       </c>
       <c r="B52">
+        <v>96</v>
+      </c>
+      <c r="C52">
+        <v>96</v>
+      </c>
+      <c r="D52" t="s">
+        <v>96</v>
+      </c>
+      <c r="E52" t="s">
+        <v>94</v>
+      </c>
+      <c r="F52" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53">
+        <v>97</v>
+      </c>
+      <c r="C53">
+        <v>97</v>
+      </c>
+      <c r="D53" t="s">
+        <v>97</v>
+      </c>
+      <c r="E53" t="s">
         <v>95</v>
       </c>
-      <c r="C52">
-        <v>95</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="F53" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54">
+        <v>98</v>
+      </c>
+      <c r="C54">
+        <v>98</v>
+      </c>
+      <c r="D54" t="s">
+        <v>98</v>
+      </c>
+      <c r="E54" t="s">
+        <v>99</v>
+      </c>
+      <c r="F54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55">
+        <v>99</v>
+      </c>
+      <c r="C55">
+        <v>99</v>
+      </c>
+      <c r="D55" t="s">
+        <v>84</v>
+      </c>
+      <c r="E55" t="s">
+        <v>96</v>
+      </c>
+      <c r="F55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56">
+        <v>100</v>
+      </c>
+      <c r="C56">
+        <v>100</v>
+      </c>
+      <c r="D56" t="s">
+        <v>100</v>
+      </c>
+      <c r="E56" t="s">
+        <v>97</v>
+      </c>
+      <c r="F56" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57">
         <v>101</v>
       </c>
-      <c r="E52" t="s">
+      <c r="C57">
+        <v>101</v>
+      </c>
+      <c r="D57" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57" t="s">
         <v>98</v>
       </c>
-      <c r="F52" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52" t="s">
+      <c r="F57" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58">
+        <v>102</v>
+      </c>
+      <c r="C58">
+        <v>102</v>
+      </c>
+      <c r="D58" t="s">
+        <v>99</v>
+      </c>
+      <c r="E58" t="s">
+        <v>101</v>
+      </c>
+      <c r="F58" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59">
+        <v>103</v>
+      </c>
+      <c r="C59">
+        <v>103</v>
+      </c>
+      <c r="D59" t="s">
+        <v>102</v>
+      </c>
+      <c r="E59" t="s">
+        <v>103</v>
+      </c>
+      <c r="F59" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" t="s">
         <v>11</v>
       </c>
     </row>

--- a/content-sources/medical-tests-reconcile.xlsx
+++ b/content-sources/medical-tests-reconcile.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="50">
   <si>
     <t>issue_type</t>
   </si>
@@ -46,10 +46,19 @@
     <t>DUPLICATE</t>
   </si>
   <si>
+    <t>C-Reactive Protein (CRP)</t>
+  </si>
+  <si>
+    <t>Rename one occurrence in the EN sheet to disambiguate (affects URL slug).</t>
+  </si>
+  <si>
+    <t>Lipoprotein(a)</t>
+  </si>
+  <si>
     <t>Homocysteine</t>
   </si>
   <si>
-    <t>Rename one occurrence in the EN sheet to disambiguate (affects URL slug).</t>
+    <t>Thyroid Stimulating Hormone (TSH)</t>
   </si>
   <si>
     <t>Testy PCR</t>
@@ -59,6 +68,9 @@
   </si>
   <si>
     <t>EAT-26 (Eating Attitudes Test)</t>
+  </si>
+  <si>
+    <t>DASS-21 (Depression Anxiety Stress Scale)</t>
   </si>
   <si>
     <t>Morfologia krwi (CBC)</t>
@@ -525,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -586,7 +598,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -606,10 +618,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -621,7 +633,7 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -629,10 +641,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -644,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
@@ -652,10 +664,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -667,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>9</v>
@@ -675,22 +687,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
         <v>9</v>
@@ -701,16 +713,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -724,16 +736,16 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -744,22 +756,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="C10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>9</v>
@@ -767,22 +779,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="C11">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>9</v>
@@ -796,13 +808,13 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
@@ -819,13 +831,13 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -842,13 +854,13 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -865,13 +877,13 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -888,13 +900,13 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
         <v>28</v>
-      </c>
-      <c r="E16" t="s">
-        <v>29</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
@@ -911,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -934,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
@@ -957,13 +969,13 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -980,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -1003,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
@@ -1026,13 +1038,13 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
@@ -1049,13 +1061,13 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
@@ -1072,10 +1084,10 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
         <v>40</v>
@@ -1095,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
         <v>41</v>
@@ -1118,13 +1130,13 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
@@ -1141,13 +1153,13 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
@@ -1164,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
@@ -1187,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
@@ -1210,18 +1222,110 @@
         <v>0</v>
       </c>
       <c r="C30">
+        <v>96</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>101</v>
+      </c>
+      <c r="D32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>105</v>
+      </c>
+      <c r="D33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
         <v>107</v>
       </c>
-      <c r="D30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="D34" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" t="s">
         <v>9</v>
       </c>
     </row>

--- a/content-sources/medical-tests-reconcile.xlsx
+++ b/content-sources/medical-tests-reconcile.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="54">
   <si>
     <t>issue_type</t>
   </si>
@@ -100,12 +100,18 @@
     <t>Kwas moczowy</t>
   </si>
   <si>
+    <t>LFT</t>
+  </si>
+  <si>
     <t>LFT (panel)</t>
   </si>
   <si>
     <t>ACR</t>
   </si>
   <si>
+    <t>Microalbuminuria</t>
+  </si>
+  <si>
     <t>Mikroalbuminuria</t>
   </si>
   <si>
@@ -115,6 +121,9 @@
     <t>Posiew kału</t>
   </si>
   <si>
+    <t>Troponin</t>
+  </si>
+  <si>
     <t>Troponina</t>
   </si>
   <si>
@@ -140,6 +149,9 @@
   </si>
   <si>
     <t>HLA-B27</t>
+  </si>
+  <si>
+    <t>Immunoglobulins</t>
   </si>
   <si>
     <t>Immunoglobuliny</t>
@@ -926,10 +938,10 @@
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -949,10 +961,10 @@
         <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
@@ -972,10 +984,10 @@
         <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -995,10 +1007,10 @@
         <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -1018,10 +1030,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
@@ -1041,10 +1053,10 @@
         <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
@@ -1064,10 +1076,10 @@
         <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
@@ -1087,10 +1099,10 @@
         <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
@@ -1110,10 +1122,10 @@
         <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
@@ -1133,10 +1145,10 @@
         <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
@@ -1156,10 +1168,10 @@
         <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
@@ -1179,10 +1191,10 @@
         <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
@@ -1202,10 +1214,10 @@
         <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
@@ -1248,10 +1260,10 @@
         <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
@@ -1271,10 +1283,10 @@
         <v>101</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
@@ -1294,10 +1306,10 @@
         <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
@@ -1317,10 +1329,10 @@
         <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
